--- a/data/origen_destino.xlsx
+++ b/data/origen_destino.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tegen\Downloads\CVP\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tegen\Downloads\CVP\Junio\Actualización tablero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77D3522C-5073-401F-8226-24ECC928CDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA94585-1B6B-4878-B696-75EDA2ECC3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="15216" xr2:uid="{C66CAA52-7C1B-4094-A0E1-F47EB1A5F165}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja4" sheetId="4" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja4!$A$1:$K$37</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="38">
   <si>
     <t>Nombre Proyecto</t>
   </si>
@@ -559,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62562F9F-2453-4D5D-9CE9-D493777E5DAB}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -626,10 +628,11 @@
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="K2" s="2">
-        <v>180</v>
+        <f>+SUM(H2:J2)</f>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -661,10 +664,11 @@
         <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="2">
-        <v>21</v>
+        <f t="shared" ref="K3:K37" si="0">+SUM(H3:J3)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -696,10 +700,11 @@
         <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -734,6 +739,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -769,6 +775,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="2">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -804,6 +811,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -839,6 +847,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="2">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -871,10 +880,11 @@
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2">
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -909,6 +919,7 @@
         <v>7</v>
       </c>
       <c r="K10" s="2">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -940,6 +951,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -975,6 +987,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1010,6 +1023,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="2">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1045,6 +1059,7 @@
         <v>6</v>
       </c>
       <c r="K14" s="2">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1080,6 +1095,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1115,6 +1131,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1150,6 +1167,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1185,6 +1203,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="2">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1220,6 +1239,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1255,6 +1275,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
@@ -1290,6 +1311,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1325,6 +1347,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1360,6 +1383,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1395,6 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1430,6 +1455,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1465,6 +1491,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1500,6 +1527,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="2">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
@@ -1535,23 +1563,28 @@
         <v>0</v>
       </c>
       <c r="K28" s="2">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C29" s="5">
+        <v>4625914</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-74220515</v>
+      </c>
       <c r="E29" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>12</v>
@@ -1560,106 +1593,110 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="2">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="4" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
       </c>
       <c r="K31" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H32" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
       </c>
       <c r="K32" s="2">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -1678,10 +1715,10 @@
         <v>29</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H33" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I33" s="2">
         <v>0</v>
@@ -1690,7 +1727,8 @@
         <v>0</v>
       </c>
       <c r="K33" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -1709,10 +1747,10 @@
         <v>29</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
@@ -1721,7 +1759,8 @@
         <v>0</v>
       </c>
       <c r="K34" s="2">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -1740,10 +1779,10 @@
         <v>29</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H35" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
@@ -1752,7 +1791,8 @@
         <v>0</v>
       </c>
       <c r="K35" s="2">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -1771,18 +1811,51 @@
         <v>29</v>
       </c>
       <c r="G36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="2">
+        <v>11</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="2">
-        <v>1</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
